--- a/backtest_runs/20260410_193731/by_symbol/HBLTETF/HBLTETF.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/HBLTETF/HBLTETF.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -587,7 +587,7 @@
         <v>-108.9600000000041</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" s="3" t="n">
         <v>100000</v>
@@ -679,7 +679,7 @@
         <v>-90.79999999999484</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>100000</v>
@@ -817,7 +817,7 @@
         <v>-54.48000000000206</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>100127.12</v>
@@ -955,7 +955,7 @@
         <v>-90.79999999999484</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K11" s="3" t="n">
         <v>100181.6</v>
@@ -1001,7 +1001,7 @@
         <v>-54.48000000000206</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K12" s="3" t="n">
         <v>100127.12</v>
@@ -1139,7 +1139,7 @@
         <v>-72.64000000001136</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K15" s="3" t="n">
         <v>100290.56</v>
@@ -1277,7 +1277,7 @@
         <v>-45.39999999999742</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>100408.6</v>
@@ -1323,7 +1323,7 @@
         <v>-127.1200000000005</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K19" s="3" t="n">
         <v>100281.48</v>
@@ -1415,7 +1415,7 @@
         <v>-45.39999999999742</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>100408.6</v>
